--- a/docs/métricas/Cuaderno_de_Ingeniería_ERGT.xlsx
+++ b/docs/métricas/Cuaderno_de_Ingeniería_ERGT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edgar\Escritorio\ProyectoFinal\Proyecto_final-Evaluador_de_expresiones\docs\métricas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7BC0A7-408E-40EE-BB21-0A737FF4D65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09A612B-9F8A-4879-ADA6-1BB6D7B31962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="750" activeTab="1" xr2:uid="{C1997AC8-5B39-4BCD-9989-DDD67DFA5BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="750" firstSheet="1" activeTab="1" xr2:uid="{C1997AC8-5B39-4BCD-9989-DDD67DFA5BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="63">
   <si>
     <t>Estudiante: Edgar Raymundo González Torres</t>
   </si>
@@ -128,9 +128,6 @@
     <t>Nombre: Edgar Raymundo González Torres</t>
   </si>
   <si>
-    <t xml:space="preserve">Fecha: </t>
-  </si>
-  <si>
     <t>PSP</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>Fecha de apertura</t>
   </si>
   <si>
-    <t>Fecha de cierre</t>
-  </si>
-  <si>
     <t>Numero de Semanas (numero anterior + 1): 2</t>
   </si>
   <si>
@@ -237,6 +231,22 @@
   </si>
   <si>
     <t>Fecha: 11/05/2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fecha de cierre </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 17/05/2026</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -434,8 +444,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -452,8 +462,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -821,7 +831,7 @@
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="8"/>
       <c r="M3" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N3" s="22"/>
       <c r="O3" s="9"/>
@@ -849,7 +859,7 @@
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="8"/>
       <c r="H9" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" s="18"/>
       <c r="O9" s="9"/>
@@ -857,7 +867,7 @@
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="8"/>
       <c r="G10" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
@@ -899,11 +909,11 @@
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
       <c r="F19" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I19" s="20"/>
       <c r="J19" s="20"/>
@@ -913,12 +923,12 @@
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="8"/>
       <c r="E20" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
       <c r="H20" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
@@ -939,15 +949,16 @@
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="8"/>
       <c r="G23" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H23" s="18"/>
       <c r="I23" s="10">
         <v>46125</v>
       </c>
-      <c r="K23" s="18" t="s">
-        <v>38</v>
-      </c>
+      <c r="J23" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K23" s="18"/>
       <c r="L23" s="18"/>
       <c r="O23" s="9"/>
     </row>
@@ -996,12 +1007,12 @@
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="H20:N20"/>
     <mergeCell ref="G23:H23"/>
-    <mergeCell ref="K23:L23"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:K19"/>
+    <mergeCell ref="J23:L23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H20" r:id="rId1" xr:uid="{8616D2B0-5413-4127-8ED4-89AFBFEAADAD}"/>
@@ -1024,24 +1035,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="14"/>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="14"/>
       <c r="F3" s="1" t="s">
         <v>2</v>
@@ -1061,7 +1072,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>7</v>
@@ -1094,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1116,10 +1127,10 @@
         <v>60</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1139,10 +1150,10 @@
         <v>86</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -1164,10 +1175,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1189,13 +1200,13 @@
         <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="H10" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
@@ -1219,7 +1230,7 @@
         <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1239,10 +1250,10 @@
         <v>60</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1264,10 +1275,10 @@
         <v>60</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1289,13 +1300,13 @@
         <v>225</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
@@ -1318,13 +1329,13 @@
         <v>270</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
@@ -1347,10 +1358,10 @@
         <v>280</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1372,10 +1383,10 @@
         <v>310</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1397,13 +1408,13 @@
         <v>190</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
@@ -1424,13 +1435,13 @@
         <v>120</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="H19" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
@@ -1463,32 +1474,32 @@
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="G1" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -1627,7 +1638,7 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="E13" s="18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
@@ -1635,12 +1646,12 @@
       <c r="I13" s="18"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -1695,12 +1706,12 @@
       <c r="I19" s="1"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -1801,32 +1812,32 @@
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="G1" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -1965,7 +1976,7 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="E13" s="18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
@@ -1973,12 +1984,12 @@
       <c r="I13" s="18"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -2049,12 +2060,12 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -2163,32 +2174,32 @@
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="G1" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -2333,7 +2344,7 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="E13" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
@@ -2341,12 +2352,12 @@
       <c r="I13" s="18"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -2425,12 +2436,12 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -2551,32 +2562,32 @@
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="G1" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -2737,7 +2748,7 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="E13" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
@@ -2745,12 +2756,12 @@
       <c r="I13" s="18"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -2837,12 +2848,12 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -2980,32 +2991,32 @@
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="G1" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -3159,7 +3170,7 @@
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="E13" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
@@ -3167,12 +3178,12 @@
       <c r="I13" s="18"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -3275,12 +3286,12 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -3409,21 +3420,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010045991DD22A674E4289B6D49668754471" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a5657d3d79920665bd27b070e8c09c67">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="89fa5a28-2927-4133-98de-35c915d0ec2e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f168e046167dddd8ab5d6f4e6589c5eb" ns3:_="">
     <xsd:import namespace="89fa5a28-2927-4133-98de-35c915d0ec2e"/>
@@ -3625,31 +3621,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B4E7623-F9CE-4024-BD73-C6D0B89FDCEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="89fa5a28-2927-4133-98de-35c915d0ec2e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E27DF74-3977-4026-94CC-EDCCFFFB69B9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8CA2469-B2DF-4F11-9226-0A04D67A3AC5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3665,4 +3652,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E27DF74-3977-4026-94CC-EDCCFFFB69B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B4E7623-F9CE-4024-BD73-C6D0B89FDCEB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="89fa5a28-2927-4133-98de-35c915d0ec2e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>